--- a/data/evaluation_results_5.xlsx
+++ b/data/evaluation_results_5.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Metadata" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Runs'!$A$1:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Runs'!$A$1:$J$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Prompts'!$A$1:$B$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Scores'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Scores'!$A$1:$B$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Metadata'!$A$1:$B$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -439,11 +439,10 @@
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,25 +478,20 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ttft_seconds</t>
+          <t>total_latency_seconds</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>total_latency_seconds</t>
+          <t>input_tokens</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>input_tokens</t>
+          <t>output_tokens</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>output_tokens</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>error</t>
         </is>
@@ -525,29 +519,25 @@
           <t>Based on the information provided, the most likely consequence for the student who is caught wearing a non-uniform would be:
 1. Detention or time-out: The student would likely receive a detention or be sent to a designated area for a set period of time as a consequence for not following the uniform policy.
 2. Verbal warning or reminder: The student may receive a verbal warning or reminder from a teacher or school administrator about the importance of adhering to the uniform policy.
-3. Parent contact: Depending on the school's policies, the student's parents or guardians may be contacted and informed about the infraction, and they may be asked to speak with the student about the importance of following the uniform policy.
-It's unlikely that the student would face more severe consequences, such as suspension or expulsion, unless the school has a specific policy in place for repeated offenses or other circumstances.
-Note that the specific consequence would depend on the school's policies and procedures, as well as the student's individual circumstances.</t>
+3. Parent contact: In some cases, the student may be required to contact their parents or guardians to inform them of the infraction and to discuss the consequences.
+It's worth noting that the specific consequence would depend on the school's policies and the discretion of the teacher or school administrator.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:01:10.858074+00:00</t>
+          <t>2026-10-22T04:33:00.337104+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2.440971115000139</v>
+        <v>1.457754792999822</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>2.469901573000016</v>
+        <v>93</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>202</v>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
+        <v>155</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -569,31 +559,27 @@
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Based on the information provided, the most likely consequence for the student who is caught wearing a non-uniform would be:
-1. Detention or time-out: The student would likely receive a detention or be sent to a designated area for a set period of time to reflect on their actions.
-2. Verbal warning or reminder: The student may receive a verbal warning or reminder from the teacher or school administrator about the importance of wearing the uniform.
-3. Parent contact: The student's parents or guardians may be contacted to discuss the incident and the student's understanding of the uniform policy.
-It's unlikely that the student would face more severe consequences, such as suspension or expulsion, unless the school has a specific policy in place for repeated offenses or if the student's behavior is deemed to be a serious disruption to the learning environment.
-However, without more information about the specific school's policies and procedures, it's difficult to provide a definitive answer.</t>
+1. Detention or time-out: The student would likely receive a detention or be sent to a designated area for a set period of time as a consequence for not following the school's uniform policy.
+2. Verbal warning or reminder: The student may receive a verbal warning or reminder from a teacher or school administrator about the importance of adhering to the uniform policy.
+3. Parent contact: In some cases, the student's parents or guardians may be contacted and informed about the infraction, and they may be asked to speak with their child about the importance of following the uniform policy.
+It's worth noting that the specific consequence would depend on the school's policies and the discretion of the teacher or school administrator.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:01:13.328443+00:00</t>
+          <t>2026-10-22T04:33:01.795280+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1.729131993999999</v>
+        <v>1.524392224999701</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1.76774169600003</v>
+        <v>93</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>189</v>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
+        <v>168</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -616,29 +602,26 @@
         <is>
           <t>Based on the information provided, the most likely consequence for the student who is caught wearing a non-uniform would be:
 1. Detention or time-out: The student would likely receive a detention or be sent to a designated area for a set period of time as a consequence for not following the uniform policy.
-2. Verbal warning or reminder: The student may receive a verbal warning or reminder from the teacher or school administrator about the importance of following the uniform policy.
-3. Parent contact: Depending on the school's policy, the student's parents or guardians may be contacted and informed about the infraction, and may be required to discuss the issue with the student.
-It's worth noting that the specific consequence would depend on the school's policies and the student's age and behavior.</t>
+2. Verbal warning or reminder: The student may receive a verbal warning or reminder from the teacher or school administrator about the importance of adhering to the uniform policy.
+3. Parent contact: In some cases, the student's parent or guardian may be contacted to discuss the incident and the student's failure to comply with the uniform policy.
+It's worth noting that the specific consequence would depend on the school's policies and the discretion of the teacher or school administrator.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:01:15.096591+00:00</t>
+          <t>2026-10-22T04:33:03.320046+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1.494933532000005</v>
+        <v>1.574739260000115</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1.520479432999991</v>
+        <v>93</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>158</v>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
+        <v>156</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -674,22 +657,19 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:01:16.617330+00:00</t>
+          <t>2026-10-22T04:33:04.895118+00:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1.474138382000092</v>
+        <v>1.377927967999767</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1.495244343000195</v>
+        <v>90</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="J5" s="2" t="n">
         <v>148</v>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -725,22 +705,19 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:01:18.112799+00:00</t>
+          <t>2026-10-22T04:33:06.273252+00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1.37435587899995</v>
+        <v>1.365053016000275</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1.392964452999877</v>
+        <v>90</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="J6" s="2" t="n">
         <v>148</v>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -776,22 +753,19 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:01:19.506001+00:00</t>
+          <t>2026-10-22T04:33:07.638535+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1.46107143800009</v>
+        <v>1.377254666999761</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1.477873317000103</v>
+        <v>90</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="J7" s="2" t="n">
         <v>148</v>
       </c>
-      <c r="K7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -813,34 +787,29 @@
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>To solve this problem, let's break it down step by step.
-The snail climbs 3 feet up during the day, but slips back 2 feet at night, so it effectively moves 1 foot up each day (3 - 2 = 1).
-Since the well is 20 feet deep, we need to find out how many days it will take for the snail to climb 19 feet (since it will reach the top on the 20th foot).
-To find the number of days, we can divide the total distance (19 feet) by the daily progress (1 foot):
-19 feet / 1 foot/day = 19 days
-However, this calculation only accounts for the days when the snail climbs. We need to add 1 more day to account for the day it reaches the top (20 feet).
-So, the total number of days it will take for the snail to reach the top of the well is:
-19 days + 1 day = 20 days
-Therefore, it will take the snail 20 days to reach the top of the 20-foot well.</t>
+The snail climbs 3 feet up during the day and slips back 2 feet at night, so it effectively moves 1 foot up the well each day (3 - 2 = 1).
+Since the well is 20 feet deep, the snail needs to cover 20 feet to reach the top.
+To find the number of days it will take for the snail to reach the top, we can divide the total depth of the well (20 feet) by the daily progress of the snail (1 foot).
+20 feet / 1 foot per day = 20 days
+However, this calculation assumes that the snail will climb the entire 20 feet on the final day, which is not the case. On the 20th day, the snail will climb 3 feet and reach the top of the well, but it will not slip back 2 feet because it has already reached the top.
+Therefore, the correct answer is 20 days, but the snail will reach the top on the 20th day, not on the 19th day.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:01:20.984092+00:00</t>
+          <t>2026-10-22T04:33:09.016026+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>2.183716537000009</v>
+        <v>2.72130093800024</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>2.211024784000074</v>
+        <v>112</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>112</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>227</v>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
+        <v>235</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -863,33 +832,30 @@
         <is>
           <t>To solve this problem, we need to calculate the net progress of the snail each day.
 The snail climbs 3 feet up during the day, but slips back 2 feet at night, so the net progress is:
-3 (up) - 2 (down) = 1 foot
+3 feet (up) - 2 feet (down) = 1 foot
 This means the snail effectively moves 1 foot up the well each day.
 Since the well is 20 feet deep, we need to find out how many days it will take for the snail to cover this distance.
 To do this, we can divide the total depth of the well (20 feet) by the net progress of the snail (1 foot) per day:
 20 feet / 1 foot/day = 20 days
-However, this calculation assumes that the snail will climb the final 3 feet to the top on the 20th day, without slipping back. Since the snail will slip back 2 feet on the 20th day, it will only reach the top of the 19th foot.
-On the 20th day, the snail will climb the final 3 feet to reach the top of the well. Therefore, it will take the snail 20 days to reach the top of the well.</t>
+However, this calculation assumes that the snail will climb the final 3 feet to the top on the 20th day, without slipping back. Since the snail will slip back 2 feet on the 20th day, it will only reach the top of the well on the 20th day, but not climb the final 3 feet.
+So, the snail will reach the top of the well on the 20th day, but it will not climb the final 3 feet. Therefore, the correct answer is 20 days, but the snail will not reach the top of the well on the 20th day, it will reach the 19th foot on the 20th day.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:01:23.195361+00:00</t>
+          <t>2026-10-22T04:33:11.737563+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>2.297904701999869</v>
+        <v>2.646540415000345</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>2.326136972999848</v>
+        <v>112</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>112</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>255</v>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
+        <v>299</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -910,38 +876,34 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>To solve this problem, we need to consider the net progress the snail makes each day.
-The snail climbs 3 feet up during the day, but slips back 2 feet at night, so its net progress is:
-3 feet (up) - 2 feet (down) = 1 foot
-This means the snail effectively moves 1 foot up the well each day.
-Since the well is 20 feet deep, we need to find out how many days it will take for the snail to cover this distance.
-To do this, we can divide the total depth of the well (20 feet) by the net progress the snail makes each day (1 foot):
-20 feet / 1 foot/day = 20 days
-However, this calculation assumes that the snail will climb out of the well on the 20th day, but it will actually reach the top on the 20th day because it climbs 3 feet on the 20th day and reaches the top.
-Therefore, it will take the snail 20 days to reach the top of the well.</t>
+          <t>To solve this problem, let's break it down step by step.
+The snail climbs 3 feet up during the day, but slips back 2 feet at night. This means the snail effectively moves 1 foot up the well each day (3 feet up - 2 feet back).
+Since the well is 20 feet deep, we need to find out how many days it will take for the snail to climb 19 feet (since it will reach the top on the 20th foot).
+To do this, we can divide the total distance (19 feet) by the daily progress (1 foot):
+19 feet / 1 foot per day = 19 days
+However, this calculation assumes that the snail will climb 3 feet up on the 20th day and reach the top. But since the snail will slip back 2 feet at night, it will only climb 1 foot up on the 20th day.
+So, on the 20th day, the snail will reach the top of the well, but it will take 19 days of progress and 1 day of slipping back to reach the top.
+Therefore, the snail will reach the top of the well in 20 days.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:01:25.521767+00:00</t>
+          <t>2026-10-22T04:33:14.384534+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1.997000983999897</v>
+        <v>2.277873098000327</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>2.030762375999984</v>
+        <v>112</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>112</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>223</v>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+        <v>252</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K10"/>
+  <autoFilter ref="A1:J10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1013,7 +975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1041,10 +1003,12 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>{
-  "median_ttft": 1.4949335320000046,
-  "median_latency": 1.5204794329999913,
-  "correct_frequency": 0.75,
-  "misinformation_frequency": 0
+  "median_input": 91,
+  "median_output": 149,
+  "median_latency": 2.3778730980003275,
+  "correct_frequency": 0.5,
+  "misinformation_frequency": 0,
+  "relevance_frequency": 0.5
 }</t>
         </is>
       </c>
@@ -1052,45 +1016,65 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>median_ttft</t>
+          <t>median_input</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1.494933532000005</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>median_latency</t>
+          <t>median_output</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.520479432999991</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>correct_frequency</t>
+          <t>median_latency</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.75</v>
+        <v>2.377873098000328</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>correct_frequency</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t>misinformation_frequency</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B7" s="2" t="n">
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>relevance_frequency</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:B8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1128,7 +1112,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:01:29.395888+00:00</t>
+          <t>2026-10-22T04:33:18.257065+00:00</t>
         </is>
       </c>
     </row>
